--- a/docs/quality/Technical Debt Register/Technical Debt Register v0.1.xlsx
+++ b/docs/quality/Technical Debt Register/Technical Debt Register v0.1.xlsx
@@ -706,17 +706,17 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Group membership grants nothing. An Administrator can define groups (once FR-1.6 administration exists) with no effect on access.</t>
+          <t>Group membership grants nothing. An Administrator can define groups (once FR-1.6 administration exists) with no effect on access. When repaid, a further consequence follows: a group permission can admit a non-staff user at DEC-012 enforcement point 1 (the route guard), but enforcement point 2 (mayActOnRequest) is role-based and refuses every non-staff actor, so for non-staff users the union would admit at one point and refuse at the next. Points 1 and 2 would disagree. Recorded here as a consequence, not as an open item.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>req.actor already carries groupIds (DEC-018 §4), read from users on every request.</t>
+          <t>req.actor already carries groupIds (DEC-018 §4), read from users on every request. Security-category protection (FR-1.5) holds today ONLY because groups cannot carry roles and both mayActOnRequest and mayViewRequest check the Security Officer role BEFORE category authorisation. DB-01 §3.7 does not itself scope the union away from security categories. Enforced by test, not by memory: two TD-002 constraint tests in tests/authorisationGuard.test.js fail if the role-first check is removed from either predicate (commit 4921f4c; negative verification NV-23, NV-24).</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>The rule change is inside src/domain/accessRules.js under DEC-012. groupIds alone does not carry permissions: the groups documents must also be read per request (no caching, NFR-2.7) by a component with repository access, and where that read happens is part of the repayment. The accessRules tests gain group cases, negative-verified.</t>
+          <t>The rule change is inside src/domain/accessRules.js under DEC-012. groupIds alone does not carry permissions: the groups documents must also be read per request (no caching, NFR-2.7) by a component with repository access, and where that read happens is part of the repayment. CONSTRAINT ON REPAYMENT: the role-first Security Officer check must be preserved in both predicates, and the TD-002 constraint tests must still pass unchanged. The accessRules tests gain group cases, negative-verified.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
